--- a/胎壓檢測器資料庫_V10/AUDI_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/AUDI_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J928"/>
+  <dimension ref="A1:J930"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33369,32 +33369,32 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>V12 TDI Quattro</t>
+          <t>TDI quattro 180kW</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2010-01</t>
+          <t>2026-01 ~ 至今</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>AAM</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>01/2005 - 12/2014</t>
+          <t>03/2026 -</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -33421,12 +33421,12 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>e-tron 3.0 TDI quattro</t>
+          <t>TDI quattro 220kW</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2019-01</t>
+          <t>2026-01 ~ 至今</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
@@ -33436,17 +33436,17 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>BGJ, BHI</t>
+          <t>CGD</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>01/2015 - 02/2026</t>
+          <t>03/2026 -</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -33468,37 +33468,37 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>45 TDI Quattro</t>
+          <t>V12 TDI Quattro</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2009-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>BPQ</t>
+          <t>AAM</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>01/2005 - 12/2014</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -33520,17 +33520,17 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>50 TDI Quattro</t>
+          <t>e-tron 3.0 TDI quattro</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2018-01 ~ 至今</t>
+          <t>2015-01 ~ 2019-01</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
@@ -33540,12 +33540,12 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>BNL</t>
+          <t>BGJ, BHI</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>01/2015 - 02/2026</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -33577,12 +33577,12 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>50 TFSI Quattro</t>
+          <t>45 TDI Quattro</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
@@ -33592,7 +33592,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>CDD</t>
+          <t>BPQ</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -33629,12 +33629,12 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>55 TFSI Quattro</t>
+          <t>50 TDI Quattro</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
@@ -33644,7 +33644,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>BPV</t>
+          <t>BNL</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -33681,12 +33681,12 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>55 TFSI e Quattro</t>
+          <t>50 TFSI Quattro</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
@@ -33696,7 +33696,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>BXJ</t>
+          <t>CDD</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -33733,12 +33733,12 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>60 TFSI e Quattro</t>
+          <t>55 TFSI Quattro</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>BXL</t>
+          <t>BPV</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -33780,17 +33780,17 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Q8 e-tron</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>50 Quattro</t>
+          <t>55 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
@@ -33800,12 +33800,12 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>BXJ</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>09/2018 -</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -33832,17 +33832,17 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Q8 e-tron</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>55 Quattro</t>
+          <t>60 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
@@ -33852,12 +33852,12 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>CAJ</t>
+          <t>BXL</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>09/2018 -</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -33889,12 +33889,12 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>50 Quattro</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -33904,7 +33904,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>CDR</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -33936,7 +33936,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Q8 e-tron Dakar</t>
+          <t>Q8 e-tron</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -33946,7 +33946,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CAJ</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -33988,17 +33988,17 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Q8 e-tron Sportback</t>
+          <t>Q8 e-tron</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>50 Quattro</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>CDR</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -34040,7 +34040,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Q8 e-tron Sportback</t>
+          <t>Q8 e-tron Dakar</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -34050,7 +34050,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -34060,7 +34060,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>CAK</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -34097,12 +34097,12 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Competition</t>
+          <t>50 Quattro</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>CDQ</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -34144,37 +34144,37 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>R8 Coupe</t>
+          <t>Q8 e-tron Sportback</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>4.2 FSI Quattro</t>
+          <t>55 Quattro</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>2007-01 ~ 2015-01</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>AAI, AAR</t>
+          <t>CAK</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>01/2006 -, 01/2009 -</t>
+          <t>01/2019 -</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -34196,37 +34196,37 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>R8 Coupe</t>
+          <t>Q8 e-tron Sportback</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>5.2 FSI LMX</t>
+          <t>Competition</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2015-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>CDQ</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>01/2009 -</t>
+          <t>01/2019 -</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>5.2 FSI V10 Plus Quattro</t>
+          <t>4.2 FSI Quattro</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2015-01</t>
+          <t>2007-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
@@ -34268,12 +34268,12 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>AAW</t>
+          <t>AAI, AAR</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>01/2009 -</t>
+          <t>01/2006 -, 01/2009 -</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -34305,12 +34305,12 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>5.2 FSI V10 Quattro</t>
+          <t>5.2 FSI LMX</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2015-01</t>
+          <t>2014-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
@@ -34320,7 +34320,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>AAL</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -34357,22 +34357,22 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>5.2 V10 GT RWD</t>
+          <t>5.2 FSI V10 Plus Quattro</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2012-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>ABK</t>
+          <t>AAW</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -34409,22 +34409,22 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>5.2 V10 Performance Quattro</t>
+          <t>5.2 FSI V10 Quattro</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2009-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>AAL</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -34461,12 +34461,12 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>5.2 V10 Performance RWD</t>
+          <t>5.2 V10 GT RWD</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>2021-01 ~ 至今</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>ABG</t>
+          <t>ABK</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -34513,22 +34513,22 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>5.2 V10 Plus Quattro</t>
+          <t>5.2 V10 Performance Quattro</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2018-01</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>ABH</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -34565,22 +34565,22 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>5.2 V10 Quattro</t>
+          <t>5.2 V10 Performance RWD</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2021-01</t>
+          <t>2021-01 ~ 至今</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>7967, 1860</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>ABG, AAU</t>
+          <t>ABG</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -34617,12 +34617,12 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>5.2 V10 Quattro GT</t>
+          <t>5.2 V10 Plus Quattro</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>2010-01 ~ 2012-01</t>
+          <t>2015-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
@@ -34632,7 +34632,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>AAQ</t>
+          <t>ABH</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -34669,22 +34669,22 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>5.2 V10 RWD</t>
+          <t>5.2 V10 Quattro</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2021-01</t>
+          <t>2015-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967, 1860</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>AAQ</t>
+          <t>ABG, AAU</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -34721,12 +34721,12 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>e-tron</t>
+          <t>5.2 V10 Quattro GT</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2018-01</t>
+          <t>2010-01 ~ 2012-01</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>ABP</t>
+          <t>AAQ</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -34768,27 +34768,27 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>R8 Spyder</t>
+          <t>R8 Coupe</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>4.2 FSI Quattro</t>
+          <t>5.2 V10 RWD</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>2010-01 ~ 2015-01</t>
+          <t>2019-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>AAQ</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -34820,17 +34820,17 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>R8 Spyder</t>
+          <t>R8 Coupe</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>5.2 FSI LMX</t>
+          <t>e-tron</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2015-01</t>
+          <t>2016-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>ABD</t>
+          <t>ABP</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -34877,12 +34877,12 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>5.2 FSI V10 Plus Quattro</t>
+          <t>4.2 FSI Quattro</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2015-01</t>
+          <t>2010-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -34929,12 +34929,12 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>5.2 FSI V10 Quattro</t>
+          <t>5.2 FSI LMX</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>2010-01 ~ 2015-01</t>
+          <t>2014-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>AAN</t>
+          <t>ABD</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -34981,22 +34981,22 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>5.2 V10 Performance Quattro</t>
+          <t>5.2 FSI V10 Plus Quattro</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2013-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>AAV</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -35033,22 +35033,22 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>5.2 V10 Performance RWD</t>
+          <t>5.2 FSI V10 Quattro</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>2021-01 ~ 至今</t>
+          <t>2010-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>ABH</t>
+          <t>AAN</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -35085,12 +35085,12 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>5.2 V10 Plus Quattro</t>
+          <t>5.2 V10 Performance Quattro</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2018-01</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
@@ -35100,7 +35100,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>AAV</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -35137,22 +35137,22 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>5.2 V10 Quattro</t>
+          <t>5.2 V10 Performance RWD</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2021-01</t>
+          <t>2021-01 ~ 至今</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>7967, 1860</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>ABM, AAW</t>
+          <t>ABH</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -35189,22 +35189,22 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>5.2 V10 Quattro GT</t>
+          <t>5.2 V10 Plus Quattro</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>2011-01 ~ 2012-01</t>
+          <t>2017-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>AAU</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -35241,22 +35241,22 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>5.2 V10 RWD</t>
+          <t>5.2 V10 Quattro</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2021-01</t>
+          <t>2016-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967, 1860</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>AAR</t>
+          <t>ABM, AAW</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -35288,37 +35288,37 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>RS Q3</t>
+          <t>R8 Spyder</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>2.5 TFSI Quattro</t>
+          <t>5.2 V10 Quattro GT</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2025-01</t>
+          <t>2011-01 ~ 2012-01</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>7967, 1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>ABA, ABE, AAY</t>
+          <t>AAU</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>01/2009 -</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -35340,33 +35340,49 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>RS Q3</t>
+          <t>R8 Spyder</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>2.5 TFSI Quattro performance</t>
+          <t>5.2 V10 RWD</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2018-01</t>
+          <t>2019-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>ABL</t>
-        </is>
-      </c>
-      <c r="G775" t="inlineStr"/>
-      <c r="H775" t="inlineStr"/>
-      <c r="I775" t="inlineStr"/>
-      <c r="J775" t="inlineStr"/>
+          <t>AAR</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>01/2009 -</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -35376,7 +35392,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>RS Q3 Sportback</t>
+          <t>RS Q3</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -35386,17 +35402,17 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2025-01</t>
+          <t>2013-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967, 1860</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>AAZ</t>
+          <t>ABA, ABE, AAY</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -35428,49 +35444,33 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>RS Q8</t>
+          <t>RS Q3</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro</t>
+          <t>2.5 TFSI Quattro performance</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2016-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>ABC, ABV</t>
-        </is>
-      </c>
-      <c r="G777" t="inlineStr">
-        <is>
-          <t>09/2018 - 11/2024, 12/2024 -</t>
-        </is>
-      </c>
-      <c r="H777" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
-        </is>
-      </c>
-      <c r="I777" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J777" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+      <c r="J777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -35480,27 +35480,27 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>RS e-tron GT</t>
+          <t>RS Q3 Sportback</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>2.5 TFSI Quattro</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2019-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>AAZ</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -35532,37 +35532,37 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>RS e-tron GT</t>
+          <t>RS Q8</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Quattro</t>
+          <t>4.0 V8 Quattro</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>2021-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>BZM, CCD</t>
+          <t>ABC, ABV</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>09/2018 - 11/2024, 12/2024 -</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -35584,33 +35584,49 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>RS2 Avant</t>
+          <t>RS e-tron GT</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>2.2 Quattro</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>1994-01 ~ 1996-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G780" t="inlineStr"/>
-      <c r="H780" t="inlineStr"/>
-      <c r="I780" t="inlineStr"/>
-      <c r="J780" t="inlineStr"/>
+          <t>CCE</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>01/2019 -</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -35620,17 +35636,17 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>RS2 Coupe</t>
+          <t>RS e-tron GT</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>2.1 Quattro</t>
+          <t>Quattro</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>1980-01 ~ 1987-01</t>
+          <t>2021-01 ~ 至今</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -35640,13 +35656,29 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="G781" t="inlineStr"/>
-      <c r="H781" t="inlineStr"/>
-      <c r="I781" t="inlineStr"/>
-      <c r="J781" t="inlineStr"/>
+          <t>BZM, CCD</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>01/2019 -</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -35656,7 +35688,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>RS2 Coupe</t>
+          <t>RS2 Avant</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -35666,17 +35698,17 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>1987-01 ~ 1991-01</t>
+          <t>1994-01 ~ 1996-01</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>410, 479</t>
+          <t>300</t>
         </is>
       </c>
       <c r="G782" t="inlineStr"/>
@@ -35692,49 +35724,33 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>RS3 Limousine</t>
+          <t>RS2 Coupe</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>2.5 TFSI Performance Quattro</t>
+          <t>2.1 Quattro</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>2023-01 ~ 2024-01</t>
+          <t>1980-01 ~ 1987-01</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>ABJ</t>
-        </is>
-      </c>
-      <c r="G783" t="inlineStr">
-        <is>
-          <t>04/2017 -</t>
-        </is>
-      </c>
-      <c r="H783" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I783" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J783" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -35744,49 +35760,33 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>RS3 Limousine</t>
+          <t>RS2 Coupe</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>2.5 TFSI Quattro</t>
+          <t>2.2 Quattro</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>2017-01 ~ 至今</t>
+          <t>1987-01 ~ 1991-01</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>AAB, ABF</t>
-        </is>
-      </c>
-      <c r="G784" t="inlineStr">
-        <is>
-          <t>04/2017 -, 04/2017 - 01/2025, 02/2025 -</t>
-        </is>
-      </c>
-      <c r="H784" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
-        </is>
-      </c>
-      <c r="I784" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J784" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>410, 479</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -35796,7 +35796,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>RS3 Sportback</t>
+          <t>RS3 Limousine</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>ABI</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>RS3 Sportback</t>
+          <t>RS3 Limousine</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -35858,17 +35858,17 @@
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>2011-01 ~ 至今</t>
+          <t>2017-01 ~ 至今</t>
         </is>
       </c>
       <c r="E786" t="inlineStr">
         <is>
-          <t>7967, 1860</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>AAS, ABF, AAC, ABE</t>
+          <t>AAB, ABF</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -35900,37 +35900,37 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>RS4</t>
+          <t>RS3 Sportback</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>2.5 TFSI Performance Quattro</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>2005-01 ~ 2008-01</t>
+          <t>2023-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>ABI</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>01/2006 - 12/2008</t>
+          <t>04/2017 -</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -35952,33 +35952,49 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>RS4 Avant</t>
+          <t>RS3 Sportback</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>2.7 BiTurbo Quattro</t>
+          <t>2.5 TFSI Quattro</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>2000-01 ~ 2001-01</t>
+          <t>2011-01 ~ 至今</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7967, 1860</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="G788" t="inlineStr"/>
-      <c r="H788" t="inlineStr"/>
-      <c r="I788" t="inlineStr"/>
-      <c r="J788" t="inlineStr"/>
+          <t>AAS, ABF, AAC, ABE</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>04/2017 -, 04/2017 - 01/2025, 02/2025 -</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -35988,37 +36004,37 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>RS4 Avant</t>
+          <t>RS4</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>2.9 V6-Biturbo</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2024-01</t>
+          <t>2005-01 ~ 2008-01</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>AAS</t>
+          <t>321</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>09/2017 -</t>
+          <t>01/2006 - 12/2008</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -36045,44 +36061,28 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>2.9 V6-Biturbo 25 Years Edition</t>
+          <t>2.7 BiTurbo Quattro</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>2024-01 ~ 2024-01</t>
+          <t>2000-01 ~ 2001-01</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>ABW</t>
-        </is>
-      </c>
-      <c r="G790" t="inlineStr">
-        <is>
-          <t>09/2017 -</t>
-        </is>
-      </c>
-      <c r="H790" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I790" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J790" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="inlineStr"/>
+      <c r="J790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -36097,28 +36097,44 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>4.2 FSI Quattro</t>
+          <t>2.9 V6-Biturbo</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2015-01</t>
+          <t>2017-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>AAV</t>
-        </is>
-      </c>
-      <c r="G791" t="inlineStr"/>
-      <c r="H791" t="inlineStr"/>
-      <c r="I791" t="inlineStr"/>
-      <c r="J791" t="inlineStr"/>
+          <t>AAS</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>09/2017 -</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -36133,32 +36149,32 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>2.9 V6-Biturbo 25 Years Edition</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>2005-01 ~ 2008-01</t>
+          <t>2024-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>01/2006 - 12/2008</t>
+          <t>09/2017 -</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -36180,17 +36196,17 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>RS4 Cabrio</t>
+          <t>RS4 Avant</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>4.2 FSI Quattro</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2008-01</t>
+          <t>2012-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
@@ -36200,29 +36216,13 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>AAH</t>
-        </is>
-      </c>
-      <c r="G793" t="inlineStr">
-        <is>
-          <t>01/2006 - 12/2008</t>
-        </is>
-      </c>
-      <c r="H793" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I793" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J793" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AAV</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -36232,37 +36232,37 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>RS5 Avant</t>
+          <t>RS4 Avant</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>TFSI quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>2026-01 ~ 至今</t>
+          <t>2005-01 ~ 2008-01</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>ACB</t>
+          <t>322</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>12/2024 -</t>
+          <t>01/2006 - 12/2008</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -36284,7 +36284,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>RS5 Cabrio</t>
+          <t>RS4 Cabrio</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -36294,7 +36294,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2015-01</t>
+          <t>2006-01 ~ 2008-01</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
@@ -36304,13 +36304,29 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>AAX</t>
-        </is>
-      </c>
-      <c r="G795" t="inlineStr"/>
-      <c r="H795" t="inlineStr"/>
-      <c r="I795" t="inlineStr"/>
-      <c r="J795" t="inlineStr"/>
+          <t>AAH</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>01/2006 - 12/2008</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -36320,17 +36336,17 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>RS5 Coupe</t>
+          <t>RS5 Avant</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>2.9 TFSI V6</t>
+          <t>TFSI quattro</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2019-01</t>
+          <t>2026-01 ~ 至今</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
@@ -36340,17 +36356,17 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>AAO</t>
+          <t>ACB</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>04/2017 -</t>
+          <t>12/2024 -</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -36372,49 +36388,33 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>RS5 Coupe</t>
+          <t>RS5 Cabrio</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>2.9 V6-Biturbo</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2024-01</t>
+          <t>2013-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>AAO</t>
-        </is>
-      </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>04/2017 -</t>
-        </is>
-      </c>
-      <c r="H797" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I797" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J797" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AAX</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -36429,17 +36429,17 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>2.9 TFSI V6</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>2010-01 ~ 2015-01</t>
+          <t>2017-01 ~ 2019-01</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
@@ -36447,10 +36447,26 @@
           <t>AAO</t>
         </is>
       </c>
-      <c r="G798" t="inlineStr"/>
-      <c r="H798" t="inlineStr"/>
-      <c r="I798" t="inlineStr"/>
-      <c r="J798" t="inlineStr"/>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>04/2017 -</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -36460,17 +36476,17 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>RS5 Limousine</t>
+          <t>RS5 Coupe</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>TFSI quattro</t>
+          <t>2.9 V6-Biturbo</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>2026-01 ~ 至今</t>
+          <t>2020-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E799" t="inlineStr">
@@ -36480,17 +36496,17 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>ACA</t>
+          <t>AAO</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>12/2024 -</t>
+          <t>04/2017 -</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -36512,49 +36528,33 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>RS5 Sportback</t>
+          <t>RS5 Coupe</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>2.9 V6-Biturbo</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2024-01</t>
+          <t>2010-01 ~ 2015-01</t>
         </is>
       </c>
       <c r="E800" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>AAX</t>
-        </is>
-      </c>
-      <c r="G800" t="inlineStr">
-        <is>
-          <t>04/2017 -, 09/2017 -</t>
-        </is>
-      </c>
-      <c r="H800" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I800" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J800" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AAO</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -36564,17 +36564,17 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>RS5 Sportback</t>
+          <t>RS5 Limousine</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>2.9 V6-Biturbo Performance</t>
+          <t>TFSI quattro</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>2024-01 ~ 2024-01</t>
+          <t>2026-01 ~ 至今</t>
         </is>
       </c>
       <c r="E801" t="inlineStr">
@@ -36584,17 +36584,17 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>ABX</t>
+          <t>ACA</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>09/2017 -</t>
+          <t>12/2024 -</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -36616,37 +36616,37 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>RS6</t>
+          <t>RS5 Sportback</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>5.0 V10 Quattro</t>
+          <t>2.9 V6-Biturbo</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2010-01</t>
+          <t>2019-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>AAJ</t>
+          <t>AAX</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>01/2008 - 12/2010</t>
+          <t>04/2017 -, 09/2017 -</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -36668,37 +36668,37 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>RS6 Avant</t>
+          <t>RS5 Sportback</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro</t>
+          <t>2.9 V6-Biturbo Performance</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2025-01</t>
+          <t>2024-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>7967, 1860</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>AAY, AAH, ABA</t>
+          <t>ABX</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>02/2013 -, 07/2017 -</t>
+          <t>09/2017 -</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000, RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -36720,37 +36720,37 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>RS6 Avant</t>
+          <t>RS6</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro Performance</t>
+          <t>5.0 V10 Quattro</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>2023-01 ~ 2025-01</t>
+          <t>2008-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>AAJ</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>07/2017 -, 03/2020 -</t>
+          <t>01/2008 - 12/2010</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -36777,32 +36777,32 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro performance</t>
+          <t>4.0 V8 Quattro</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2018-01</t>
+          <t>2013-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>7967, 1860</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>ABI</t>
+          <t>AAY, AAH, ABA</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>02/2013 -</t>
+          <t>02/2013 -, 07/2017 -</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE048 + RDV021 | 45.144.000, RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -36829,32 +36829,32 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>4.0 V8 Quattro Performance</t>
         </is>
       </c>
       <c r="D806" t="inlineStr">
         <is>
-          <t>2002-01 ~ 2004-01</t>
+          <t>2023-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>308, 319</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>04/2000 - 09/2005</t>
+          <t>07/2017 -, 03/2020 -</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>RDE001 + RDV021 | 73.901.101</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -36881,12 +36881,12 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>5.0 V10 Quattro</t>
+          <t>4.0 V8 Quattro performance</t>
         </is>
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2010-01</t>
+          <t>2015-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E807" t="inlineStr">
@@ -36896,12 +36896,12 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>AAK</t>
+          <t>ABI</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>01/2008 - 12/2010</t>
+          <t>02/2013 -</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -36928,17 +36928,17 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>RS7 Sportback</t>
+          <t>RS6 Avant</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2018-01</t>
+          <t>2002-01 ~ 2004-01</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -36948,17 +36948,17 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>AAZ</t>
+          <t>308, 319</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>01/2013 -</t>
+          <t>04/2000 - 09/2005</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE001 + RDV021 | 73.901.101</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -36980,17 +36980,17 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>RS7 Sportback</t>
+          <t>RS6 Avant</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro performance</t>
+          <t>5.0 V10 Quattro</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2018-01</t>
+          <t>2008-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -37000,12 +37000,12 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>ABJ</t>
+          <t>AAK</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>01/2013 -</t>
+          <t>01/2008 - 12/2010</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
@@ -37037,32 +37037,32 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2025-01</t>
+          <t>2013-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>AAZ</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>02/2018 -</t>
+          <t>01/2013 -</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -37089,32 +37089,32 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>4.0 V8 Quattro Performance</t>
+          <t>4.0 TFSI Quattro performance</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>2023-01 ~ 2025-01</t>
+          <t>2015-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>ABL</t>
+          <t>ABJ</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>02/2018 -</t>
+          <t>01/2013 -</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -37136,33 +37136,49 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>RS7 Sportback</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>4.0 V8 Quattro</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2018-01</t>
+          <t>2019-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>AZH</t>
-        </is>
-      </c>
-      <c r="G812" t="inlineStr"/>
-      <c r="H812" t="inlineStr"/>
-      <c r="I812" t="inlineStr"/>
-      <c r="J812" t="inlineStr"/>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>02/2018 -</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -37172,33 +37188,49 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>S1 Sportback</t>
+          <t>RS7 Sportback</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>4.0 V8 Quattro Performance</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2018-01</t>
+          <t>2023-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>AZI</t>
-        </is>
-      </c>
-      <c r="G813" t="inlineStr"/>
-      <c r="H813" t="inlineStr"/>
-      <c r="I813" t="inlineStr"/>
-      <c r="J813" t="inlineStr"/>
+          <t>ABL</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>02/2018 -</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -37208,17 +37240,17 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>1.8 T Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>1999-01 ~ 2003-01</t>
+          <t>2014-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -37228,7 +37260,7 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>704, 790, 815</t>
+          <t>AZH</t>
         </is>
       </c>
       <c r="G814" t="inlineStr"/>
@@ -37244,7 +37276,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S1 Sportback</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -37254,7 +37286,7 @@
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2018-01</t>
+          <t>2014-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -37264,7 +37296,7 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>AFU, AFZ, AIK, AIL, AWU, AVM, BAG, BHW, BJC</t>
+          <t>AZI</t>
         </is>
       </c>
       <c r="G815" t="inlineStr"/>
@@ -37280,17 +37312,17 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>S3 Cabrio</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>1.8 T Quattro</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2020-01</t>
+          <t>1999-01 ~ 2003-01</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -37300,7 +37332,7 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>BAS, BAT, BIJ, BJF</t>
+          <t>704, 790, 815</t>
         </is>
       </c>
       <c r="G816" t="inlineStr"/>
@@ -37316,7 +37348,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>S3 Limousine</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -37326,7 +37358,7 @@
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>2013-01 ~ 至今</t>
+          <t>2006-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -37336,7 +37368,7 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>AZB, AYD, BAN, BIE, BJD, BVG, CAY</t>
+          <t>AFU, AFZ, AIK, AIL, AWU, AVM, BAG, BHW, BJC</t>
         </is>
       </c>
       <c r="G817" t="inlineStr"/>
@@ -37352,7 +37384,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>S3 Sportback</t>
+          <t>S3 Cabrio</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -37362,7 +37394,7 @@
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>2008-01 ~ 至今</t>
+          <t>2014-01 ~ 2020-01</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -37372,7 +37404,7 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>AIK, AIL, AXY, AWO, BAK, BIA, BJE, BVH, CAZ</t>
+          <t>BAS, BAT, BIJ, BJF</t>
         </is>
       </c>
       <c r="G818" t="inlineStr"/>
@@ -37388,27 +37420,27 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3 Limousine</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>2.7 Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>1997-01 ~ 2001-01</t>
+          <t>2013-01 ~ 至今</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>7967, 0588</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>305, 645</t>
+          <t>AZB, AYD, BAN, BIE, BJD, BVG, CAY</t>
         </is>
       </c>
       <c r="G819" t="inlineStr"/>
@@ -37424,17 +37456,17 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3 Sportback</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2024-01</t>
+          <t>2008-01 ~ 至今</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -37444,7 +37476,7 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>BPX, BXV</t>
+          <t>AIK, AIL, AXY, AWO, BAK, BIA, BJE, BVH, CAZ</t>
         </is>
       </c>
       <c r="G820" t="inlineStr"/>
@@ -37465,22 +37497,22 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>2.7 Quattro</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2018-01</t>
+          <t>1997-01 ~ 2001-01</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967, 0588</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>AJV, BHQ</t>
+          <t>305, 645</t>
         </is>
       </c>
       <c r="G821" t="inlineStr"/>
@@ -37501,12 +37533,12 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>1992-01 ~ 1994-01</t>
+          <t>2019-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -37516,7 +37548,7 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>BPX, BXV</t>
         </is>
       </c>
       <c r="G822" t="inlineStr"/>
@@ -37537,12 +37569,12 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>4.2 V8 Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>2003-01 ~ 2008-01</t>
+          <t>2009-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E823" t="inlineStr">
@@ -37552,29 +37584,13 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>824, ADD</t>
-        </is>
-      </c>
-      <c r="G823" t="inlineStr">
-        <is>
-          <t>01/2004 - 12/2007</t>
-        </is>
-      </c>
-      <c r="H823" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I823" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J823" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AJV, BHQ</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+      <c r="J823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -37584,27 +37600,27 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>S4 Avant</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>2.7 Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
         <is>
-          <t>1997-01 ~ 2001-01</t>
+          <t>1992-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E824" t="inlineStr">
         <is>
-          <t>7967, 0588</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>306, 646</t>
+          <t>576</t>
         </is>
       </c>
       <c r="G824" t="inlineStr"/>
@@ -37620,17 +37636,17 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>S4 Avant</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>4.2 V8 Quattro</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2024-01</t>
+          <t>2003-01 ~ 2008-01</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
@@ -37640,13 +37656,29 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>BPY, BXU</t>
-        </is>
-      </c>
-      <c r="G825" t="inlineStr"/>
-      <c r="H825" t="inlineStr"/>
-      <c r="I825" t="inlineStr"/>
-      <c r="J825" t="inlineStr"/>
+          <t>824, ADD</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>01/2004 - 12/2007</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -37661,22 +37693,22 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>2.7 Quattro</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2018-01</t>
+          <t>1997-01 ~ 2001-01</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967, 0588</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>AJW, AMQ, APN, BHR, BKE</t>
+          <t>306, 646</t>
         </is>
       </c>
       <c r="G826" t="inlineStr"/>
@@ -37697,12 +37729,12 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>1992-01 ~ 1994-01</t>
+          <t>2019-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
@@ -37712,7 +37744,7 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>BPY, BXU</t>
         </is>
       </c>
       <c r="G827" t="inlineStr"/>
@@ -37733,12 +37765,12 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>4.2 V8 Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>2003-01 ~ 2008-01</t>
+          <t>2009-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
@@ -37748,29 +37780,13 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>824, ACN</t>
-        </is>
-      </c>
-      <c r="G828" t="inlineStr">
-        <is>
-          <t>01/2004 - 12/2007</t>
-        </is>
-      </c>
-      <c r="H828" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I828" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J828" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AJW, AMQ, APN, BHR, BKE</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr"/>
+      <c r="J828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -37780,49 +37796,33 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>S4 Cabrio</t>
+          <t>S4 Avant</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>4.2 V8 Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>2004-01 ~ 2009-01</t>
+          <t>1992-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>0588, 7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>859, 299, AET, AAD</t>
-        </is>
-      </c>
-      <c r="G829" t="inlineStr">
-        <is>
-          <t>01/2004 - 12/2007</t>
-        </is>
-      </c>
-      <c r="H829" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I829" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J829" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -37832,17 +37832,17 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>S5 Avant</t>
+          <t>S4 Avant</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>4.2 V8 Quattro</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2003-01 ~ 2008-01</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -37852,17 +37852,17 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>CBQ</t>
+          <t>824, ACN</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>12/2024 -</t>
+          <t>01/2004 - 12/2007</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -37884,33 +37884,49 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>S5 Cabrio</t>
+          <t>S4 Cabrio</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>4.2 V8 Quattro</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2018-01</t>
+          <t>2004-01 ~ 2009-01</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>0588, 7967</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>AKF, BKV</t>
-        </is>
-      </c>
-      <c r="G831" t="inlineStr"/>
-      <c r="H831" t="inlineStr"/>
-      <c r="I831" t="inlineStr"/>
-      <c r="J831" t="inlineStr"/>
+          <t>859, 299, AET, AAD</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>01/2004 - 12/2007</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -37920,17 +37936,17 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>S5 Cabrio</t>
+          <t>S5 Avant</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>55 TFSI Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2024-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
@@ -37940,17 +37956,17 @@
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>BKV</t>
+          <t>CBQ</t>
         </is>
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>08/2015 -</t>
+          <t>12/2024 -</t>
         </is>
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -37972,17 +37988,17 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>S5 Coupe</t>
+          <t>S5 Cabrio</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2024-01</t>
+          <t>2009-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E833" t="inlineStr">
@@ -37992,29 +38008,13 @@
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>BPZ, BXW</t>
-        </is>
-      </c>
-      <c r="G833" t="inlineStr">
-        <is>
-          <t>08/2015 -</t>
-        </is>
-      </c>
-      <c r="H833" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I833" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J833" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AKF, BKV</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="inlineStr"/>
+      <c r="J833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -38024,17 +38024,17 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>S5 Coupe</t>
+          <t>S5 Cabrio</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>55 TFSI Quattro</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>2011-01 ~ 2018-01</t>
+          <t>2020-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
@@ -38044,13 +38044,29 @@
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>ASC, BJB</t>
-        </is>
-      </c>
-      <c r="G834" t="inlineStr"/>
-      <c r="H834" t="inlineStr"/>
-      <c r="I834" t="inlineStr"/>
-      <c r="J834" t="inlineStr"/>
+          <t>BKV</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>08/2015 -</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -38065,12 +38081,12 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>2007-01 ~ 2011-01</t>
+          <t>2019-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
@@ -38080,13 +38096,29 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>AGA</t>
-        </is>
-      </c>
-      <c r="G835" t="inlineStr"/>
-      <c r="H835" t="inlineStr"/>
-      <c r="I835" t="inlineStr"/>
-      <c r="J835" t="inlineStr"/>
+          <t>BPZ, BXW</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>08/2015 -</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -38096,7 +38128,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>S5 Limousine</t>
+          <t>S5 Coupe</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -38106,7 +38138,7 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2011-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
@@ -38116,29 +38148,13 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>CBR</t>
-        </is>
-      </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>12/2024 -</t>
-        </is>
-      </c>
-      <c r="H836" t="inlineStr">
-        <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
-        </is>
-      </c>
-      <c r="I836" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J836" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>ASC, BJB</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="inlineStr"/>
+      <c r="J836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -38148,17 +38164,17 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>S5 Sportback</t>
+          <t>S5 Coupe</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2024-01</t>
+          <t>2007-01 ~ 2011-01</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
@@ -38168,29 +38184,13 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>BQA, BXX</t>
-        </is>
-      </c>
-      <c r="G837" t="inlineStr">
-        <is>
-          <t>08/2015 -</t>
-        </is>
-      </c>
-      <c r="H837" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I837" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J837" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AGA</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="inlineStr"/>
+      <c r="J837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>S5 Sportback</t>
+          <t>S5 Limousine</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -38210,7 +38210,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>2009-01 ~ 2018-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
@@ -38220,13 +38220,29 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>ALN, AMQ, APN, BJS, BKE</t>
-        </is>
-      </c>
-      <c r="G838" t="inlineStr"/>
-      <c r="H838" t="inlineStr"/>
-      <c r="I838" t="inlineStr"/>
-      <c r="J838" t="inlineStr"/>
+          <t>CBR</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>12/2024 -</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -38236,17 +38252,17 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5 Sportback</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>2.2 Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>1991-01 ~ 1994-01</t>
+          <t>2019-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
@@ -38256,13 +38272,29 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="G839" t="inlineStr"/>
-      <c r="H839" t="inlineStr"/>
-      <c r="I839" t="inlineStr"/>
-      <c r="J839" t="inlineStr"/>
+          <t>BQA, BXX</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>08/2015 -</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -38272,17 +38304,17 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S5 Sportback</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2025-01</t>
+          <t>2009-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
@@ -38292,29 +38324,13 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>BQG, BWU</t>
-        </is>
-      </c>
-      <c r="G840" t="inlineStr">
-        <is>
-          <t>02/2018 -, 07/2017 -</t>
-        </is>
-      </c>
-      <c r="H840" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I840" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J840" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>ALN, AMQ, APN, BJS, BKE</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr"/>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="inlineStr"/>
+      <c r="J840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -38329,12 +38345,12 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>2.2 Quattro</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2018-01</t>
+          <t>1991-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
@@ -38344,29 +38360,13 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>AVD, BBK</t>
-        </is>
-      </c>
-      <c r="G841" t="inlineStr">
-        <is>
-          <t>01/2011 - 12/2013</t>
-        </is>
-      </c>
-      <c r="H841" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I841" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J841" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr"/>
+      <c r="H841" t="inlineStr"/>
+      <c r="I841" t="inlineStr"/>
+      <c r="J841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -38381,28 +38381,44 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>4.2 Plus Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>1996-01 ~ 1997-01</t>
+          <t>2019-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="G842" t="inlineStr"/>
-      <c r="H842" t="inlineStr"/>
-      <c r="I842" t="inlineStr"/>
-      <c r="J842" t="inlineStr"/>
+          <t>BQG, BWU</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>02/2018 -, 07/2017 -</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -38417,32 +38433,32 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>1994-01 ~ 2005-01</t>
+          <t>2012-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>0588, 7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>585, 300, 707</t>
+          <t>AVD, BBK</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>01/2000 - 12/2005</t>
+          <t>01/2011 - 12/2013</t>
         </is>
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>RDE001 + RDV021 | 73.901.101</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -38469,44 +38485,28 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>5.2 Quattro</t>
+          <t>4.2 Plus Quattro</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2011-01</t>
+          <t>1996-01 ~ 1997-01</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>AAX</t>
-        </is>
-      </c>
-      <c r="G844" t="inlineStr">
-        <is>
-          <t>05/2004 - 08/2011</t>
-        </is>
-      </c>
-      <c r="H844" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I844" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J844" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="inlineStr"/>
+      <c r="J844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -38516,33 +38516,49 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>S6 Avant</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>2.2 Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>1991-01 ~ 1994-01</t>
+          <t>1994-01 ~ 2005-01</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>0588, 7967</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="G845" t="inlineStr"/>
-      <c r="H845" t="inlineStr"/>
-      <c r="I845" t="inlineStr"/>
-      <c r="J845" t="inlineStr"/>
+          <t>585, 300, 707</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>01/2000 - 12/2005</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>RDE001 + RDV021 | 73.901.101</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -38552,17 +38568,17 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>S6 Avant</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>5.2 Quattro</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2025-01</t>
+          <t>2006-01 ~ 2011-01</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
@@ -38572,17 +38588,17 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>BQE, BWV</t>
+          <t>AAX</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>02/2018 -, 07/2017 -</t>
+          <t>05/2004 - 08/2011</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -38609,12 +38625,12 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>2.2 Quattro</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2018-01</t>
+          <t>1991-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
@@ -38624,29 +38640,13 @@
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>AVC, AVY, BBU, BCH</t>
-        </is>
-      </c>
-      <c r="G847" t="inlineStr">
-        <is>
-          <t>01/2011 - 12/2013</t>
-        </is>
-      </c>
-      <c r="H847" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I847" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J847" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="inlineStr"/>
+      <c r="J847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -38661,28 +38661,44 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>4.2 Plus Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>1996-01 ~ 1997-01</t>
+          <t>2019-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="G848" t="inlineStr"/>
-      <c r="H848" t="inlineStr"/>
-      <c r="I848" t="inlineStr"/>
-      <c r="J848" t="inlineStr"/>
+          <t>BQE, BWV</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>02/2018 -, 07/2017 -</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -38697,32 +38713,32 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>1994-01 ~ 2005-01</t>
+          <t>2012-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>0588, 7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>586, 301, 708</t>
+          <t>AVC, AVY, BBU, BCH</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>01/2000 - 12/2005</t>
+          <t>01/2011 - 12/2013</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>RDE001 + RDV021 | 73.901.101</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -38749,44 +38765,28 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>5.2 Quattro</t>
+          <t>4.2 Plus Quattro</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2011-01</t>
+          <t>1996-01 ~ 1997-01</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>AAY, ANI</t>
-        </is>
-      </c>
-      <c r="G850" t="inlineStr">
-        <is>
-          <t>05/2004 - 08/2011</t>
-        </is>
-      </c>
-      <c r="H850" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I850" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J850" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="inlineStr"/>
+      <c r="J850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -38796,37 +38796,37 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>S6 Avant e-tron</t>
+          <t>S6 Avant</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>1994-01 ~ 2005-01</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>0588, 7967</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>CCA</t>
+          <t>586, 301, 708</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>09/2024 -, 2024-01 ~ 至今</t>
+          <t>01/2000 - 12/2005</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE001 + RDV021 | 73.901.101</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -38848,17 +38848,17 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>S6 Sportback e-tron</t>
+          <t>S6 Avant</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>5.2 Quattro</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2006-01 ~ 2011-01</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
@@ -38868,17 +38868,17 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>AAY, ANI</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>09/2024 -, 2024-01 ~ 至今</t>
+          <t>05/2004 - 08/2011</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -38900,17 +38900,17 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>S7 Sportback</t>
+          <t>S6 Avant e-tron</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2025-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
@@ -38920,17 +38920,17 @@
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>BQH, BWS</t>
+          <t>CCA</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>02/2018 -</t>
+          <t>09/2024 -, 2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -38952,17 +38952,17 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>S7 Sportback</t>
+          <t>S6 Sportback e-tron</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2018-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
@@ -38972,13 +38972,29 @@
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>AVE, AVY, BAV, BCH</t>
-        </is>
-      </c>
-      <c r="G854" t="inlineStr"/>
-      <c r="H854" t="inlineStr"/>
-      <c r="I854" t="inlineStr"/>
-      <c r="J854" t="inlineStr"/>
+          <t>CCB</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>09/2024 -, 2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -38988,17 +39004,17 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7 Sportback</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2019-01</t>
+          <t>2019-01 ~ 2025-01</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
@@ -39008,17 +39024,17 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>BQH, BWS</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>11/2009 - 02/2017</t>
+          <t>02/2018 -</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -39040,49 +39056,33 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S7 Sportback</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro plus</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2019-01</t>
+          <t>2012-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>1860, 7967</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>AAA, ABK</t>
-        </is>
-      </c>
-      <c r="G856" t="inlineStr">
-        <is>
-          <t>11/2009 - 02/2017</t>
-        </is>
-      </c>
-      <c r="H856" t="inlineStr">
-        <is>
-          <t>RDE048 + RDV021 | 45.144.000</t>
-        </is>
-      </c>
-      <c r="I856" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J856" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>AVE, AVY, BAV, BCH</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="inlineStr"/>
+      <c r="J856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -39097,12 +39097,12 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>4.0 TFSI e Quattro</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2012-01 ~ 2019-01</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
@@ -39112,17 +39112,17 @@
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>BRD, BUO</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>03/2017 -</t>
+          <t>11/2009 - 02/2017</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE048 + RDV021 | 45.144.000</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -39149,28 +39149,44 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>4.0 TFSI Quattro plus</t>
         </is>
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>1994-01 ~ 2002-01</t>
+          <t>2015-01 ~ 2019-01</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>7967, 0588</t>
+          <t>1860, 7967</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>302, 642, 721</t>
-        </is>
-      </c>
-      <c r="G858" t="inlineStr"/>
-      <c r="H858" t="inlineStr"/>
-      <c r="I858" t="inlineStr"/>
-      <c r="J858" t="inlineStr"/>
+          <t>AAA, ABK</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>11/2009 - 02/2017</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>RDE048 + RDV021 | 45.144.000</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -39185,12 +39201,12 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>5.2 Quattro</t>
+          <t>4.0 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2010-01</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -39200,17 +39216,17 @@
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>BRD, BUO</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>10/2002 - 07/2010</t>
+          <t>03/2017 -</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>RDE001 + RDV021 | 73.901.101</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -39237,44 +39253,28 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>50 TDI Quattro Hybrid</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>2017-01 ~ 至今</t>
+          <t>1994-01 ~ 2002-01</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>7967, 0588</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>BML</t>
-        </is>
-      </c>
-      <c r="G860" t="inlineStr">
-        <is>
-          <t>03/2017 -</t>
-        </is>
-      </c>
-      <c r="H860" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I860" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J860" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>302, 642, 721</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="inlineStr"/>
+      <c r="J860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -39289,12 +39289,12 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>55 TFSI Quattro Hybrid</t>
+          <t>5.2 Quattro</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>2017-01 ~ 至今</t>
+          <t>2006-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -39304,17 +39304,17 @@
       </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>BMK</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>03/2017 -</t>
+          <t>10/2002 - 07/2010</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE001 + RDV021 | 73.901.101</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -39341,12 +39341,12 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>60 TDI Quattro</t>
+          <t>50 TDI Quattro Hybrid</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2021-01</t>
+          <t>2017-01 ~ 至今</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -39356,7 +39356,7 @@
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>BSD</t>
+          <t>BML</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
@@ -39393,12 +39393,12 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>60 TFSI Quattro</t>
+          <t>55 TFSI Quattro Hybrid</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2017-01 ~ 至今</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
@@ -39408,7 +39408,7 @@
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BMK</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
@@ -39445,12 +39445,12 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>60 TFSI e Quattro</t>
+          <t>60 TDI Quattro</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2020-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
@@ -39460,7 +39460,7 @@
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>BQR</t>
+          <t>BSD</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
@@ -39492,12 +39492,12 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>S8 L</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>4.0 TFSI e Quattro</t>
+          <t>60 TFSI Quattro</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>BRD, BUO</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
@@ -39544,17 +39544,17 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>S8 L</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>50 TDI Quattro Hybrid</t>
+          <t>60 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>2017-01 ~ 至今</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -39564,7 +39564,7 @@
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>BML</t>
+          <t>BQR</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>55 TFSI Quattro Hybrid</t>
+          <t>4.0 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>2017-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -39616,7 +39616,7 @@
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>BMK</t>
+          <t>BRD, BUO</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
@@ -39653,12 +39653,12 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>60 TDI Quattro</t>
+          <t>50 TDI Quattro Hybrid</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2021-01</t>
+          <t>2017-01 ~ 至今</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -39668,7 +39668,7 @@
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>BSD</t>
+          <t>BML</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
@@ -39705,12 +39705,12 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>60 TFSI Quattro</t>
+          <t>55 TFSI Quattro Hybrid</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2017-01 ~ 至今</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BMK</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
@@ -39757,12 +39757,12 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>60 TFSI e Quattro</t>
+          <t>60 TDI Quattro</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2020-01 ~ 2021-01</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>BQR</t>
+          <t>BSD</t>
         </is>
       </c>
       <c r="G870" t="inlineStr">
@@ -39804,17 +39804,17 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>SQ2</t>
+          <t>S8 L</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>60 TFSI Quattro</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>2019-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
@@ -39824,13 +39824,29 @@
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>BOO</t>
-        </is>
-      </c>
-      <c r="G871" t="inlineStr"/>
-      <c r="H871" t="inlineStr"/>
-      <c r="I871" t="inlineStr"/>
-      <c r="J871" t="inlineStr"/>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>03/2017 -</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -39840,17 +39856,17 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>SQ5</t>
+          <t>S8 L</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>60 TFSI e Quattro</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2024-01</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
@@ -39860,12 +39876,12 @@
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>AWV, AWB, BDV, BQK, BVU</t>
+          <t>BQR</t>
         </is>
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>01/2016 -</t>
+          <t>03/2017 -</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -39892,17 +39908,17 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>SQ5</t>
+          <t>SQ2</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro plus</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>2015-01 ~ 2016-01</t>
+          <t>2019-01 ~ 至今</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -39912,7 +39928,7 @@
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>BEY</t>
+          <t>BOO</t>
         </is>
       </c>
       <c r="G873" t="inlineStr"/>
@@ -39933,12 +39949,12 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>3.0 TFSI Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>2013-01 ~ 2019-01</t>
+          <t>2012-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
@@ -39948,7 +39964,7 @@
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>AZC, AZO, BKX</t>
+          <t>AWV, AWB, BDV, BQK, BVU</t>
         </is>
       </c>
       <c r="G874" t="inlineStr">
@@ -39985,12 +40001,12 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>TFSI Quattro</t>
+          <t>3.0 TDI Quattro plus</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>2025-01 ~ 至今</t>
+          <t>2015-01 ~ 2016-01</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
@@ -40000,29 +40016,13 @@
       </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>CDN</t>
-        </is>
-      </c>
-      <c r="G875" t="inlineStr">
-        <is>
-          <t>01/2025 -</t>
-        </is>
-      </c>
-      <c r="H875" t="inlineStr">
-        <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
-        </is>
-      </c>
-      <c r="I875" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J875" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>BEY</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -40032,17 +40032,17 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>SQ5 Sportback</t>
+          <t>SQ5</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>3.0 TDI Quattro</t>
+          <t>3.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>2021-01 ~ 2024-01</t>
+          <t>2013-01 ~ 2019-01</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
@@ -40052,7 +40052,7 @@
       </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>BYX</t>
+          <t>AZC, AZO, BKX</t>
         </is>
       </c>
       <c r="G876" t="inlineStr">
@@ -40084,7 +40084,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>SQ5 Sportback</t>
+          <t>SQ5</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="G877" t="inlineStr">
@@ -40136,17 +40136,17 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>SQ6 SUV e-tron</t>
+          <t>SQ5 Sportback</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>3.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2021-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
@@ -40156,13 +40156,29 @@
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>CAW</t>
-        </is>
-      </c>
-      <c r="G878" t="inlineStr"/>
-      <c r="H878" t="inlineStr"/>
-      <c r="I878" t="inlineStr"/>
-      <c r="J878" t="inlineStr"/>
+          <t>BYX</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>01/2016 -</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -40172,17 +40188,17 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>SQ6 Sportback e-tron</t>
+          <t>SQ5 Sportback</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>TFSI Quattro</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2025-01 ~ 至今</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
@@ -40192,13 +40208,29 @@
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>CAV</t>
-        </is>
-      </c>
-      <c r="G879" t="inlineStr"/>
-      <c r="H879" t="inlineStr"/>
-      <c r="I879" t="inlineStr"/>
-      <c r="J879" t="inlineStr"/>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>01/2025 -</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -40208,17 +40240,17 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>SQ7</t>
+          <t>SQ6 SUV e-tron</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>4.0 TDI Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>2016-01 ~ 2023-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
@@ -40228,29 +40260,13 @@
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>BHS, BIP</t>
-        </is>
-      </c>
-      <c r="G880" t="inlineStr">
-        <is>
-          <t>01/2015 -</t>
-        </is>
-      </c>
-      <c r="H880" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I880" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J880" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>CAW</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -40260,17 +40276,17 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>SQ7</t>
+          <t>SQ6 Sportback e-tron</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>4.0 TFSI Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>2020-01 ~ 至今</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -40280,29 +40296,13 @@
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>BVK</t>
-        </is>
-      </c>
-      <c r="G881" t="inlineStr">
-        <is>
-          <t>01/2015 -, 01/2015 - 02/2026, 03/2026 -</t>
-        </is>
-      </c>
-      <c r="H881" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
-        </is>
-      </c>
-      <c r="I881" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J881" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>CAV</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -40312,7 +40312,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>SQ8</t>
+          <t>SQ7</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -40322,7 +40322,7 @@
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2023-01</t>
+          <t>2016-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -40332,12 +40332,12 @@
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>BQY</t>
+          <t>BHS, BIP</t>
         </is>
       </c>
       <c r="G882" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>01/2015 -</t>
         </is>
       </c>
       <c r="H882" t="inlineStr">
@@ -40364,7 +40364,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>SQ8</t>
+          <t>SQ7</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -40384,17 +40384,17 @@
       </c>
       <c r="F883" t="inlineStr">
         <is>
-          <t>BVL</t>
+          <t>BVK</t>
         </is>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>01/2015 -</t>
+          <t>01/2015 -, 01/2015 - 02/2026, 03/2026 -</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -40416,17 +40416,17 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>SQ8 e-tron</t>
+          <t>SQ8</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>4.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2019-01 ~ 2023-01</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
@@ -40436,12 +40436,12 @@
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>CAL</t>
+          <t>BQY</t>
         </is>
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>09/2018 -</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
@@ -40468,17 +40468,17 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>SQ8 e-tron Sportback</t>
+          <t>SQ8</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>4.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D885" t="inlineStr">
         <is>
-          <t>2023-01 ~ 至今</t>
+          <t>2020-01 ~ 至今</t>
         </is>
       </c>
       <c r="E885" t="inlineStr">
@@ -40488,12 +40488,12 @@
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>BVL</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>01/2019 -</t>
+          <t>01/2015 -</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -40520,33 +40520,49 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>TT Coupe</t>
+          <t>SQ8 e-tron</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>1.8 T</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>1998-01 ~ 2006-01</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>300, 309, 313, 314</t>
-        </is>
-      </c>
-      <c r="G886" t="inlineStr"/>
-      <c r="H886" t="inlineStr"/>
-      <c r="I886" t="inlineStr"/>
-      <c r="J886" t="inlineStr"/>
+          <t>CAL</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>01/2019 -</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -40556,33 +40572,49 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>TT Coupe</t>
+          <t>SQ8 e-tron Sportback</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>1.8 T Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>1998-01 ~ 2006-01</t>
+          <t>2023-01 ~ 至今</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>7967, 8307</t>
+          <t>0588</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>314, 301, 302, 307, 320, 312</t>
-        </is>
-      </c>
-      <c r="G887" t="inlineStr"/>
-      <c r="H887" t="inlineStr"/>
-      <c r="I887" t="inlineStr"/>
-      <c r="J887" t="inlineStr"/>
+          <t>CAM</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>01/2019 -</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -40597,12 +40629,12 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>1.8 TFSI</t>
+          <t>1.8 T</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2018-01</t>
+          <t>1998-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -40612,7 +40644,7 @@
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>ABA, ACB</t>
+          <t>300, 309, 313, 314</t>
         </is>
       </c>
       <c r="G888" t="inlineStr"/>
@@ -40633,22 +40665,22 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>2.0 TDI Quattro</t>
+          <t>1.8 T Quattro</t>
         </is>
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2014-01</t>
+          <t>1998-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7967, 8307</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>ABE</t>
+          <t>314, 301, 302, 307, 320, 312</t>
         </is>
       </c>
       <c r="G889" t="inlineStr"/>
@@ -40669,12 +40701,12 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>2.0 TDI ultra</t>
+          <t>1.8 TFSI</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2018-01</t>
+          <t>2008-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E890" t="inlineStr">
@@ -40684,7 +40716,7 @@
       </c>
       <c r="F890" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>ABA, ACB</t>
         </is>
       </c>
       <c r="G890" t="inlineStr"/>
@@ -40705,12 +40737,12 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>2.0 TDI ultra Quattro</t>
+          <t>2.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2018-01</t>
+          <t>2008-01 ~ 2014-01</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
@@ -40720,7 +40752,7 @@
       </c>
       <c r="F891" t="inlineStr">
         <is>
-          <t>ACF</t>
+          <t>ABE</t>
         </is>
       </c>
       <c r="G891" t="inlineStr"/>
@@ -40741,12 +40773,12 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>2.0 TFSI</t>
+          <t>2.0 TDI ultra</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2018-01</t>
+          <t>2014-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
@@ -40756,7 +40788,7 @@
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>AAR, ABM, ABT</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="G892" t="inlineStr"/>
@@ -40777,12 +40809,12 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>2.0 TDI ultra Quattro</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2018-01</t>
+          <t>2017-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E893" t="inlineStr">
@@ -40792,7 +40824,7 @@
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>ABC, ABO, ABU</t>
+          <t>ACF</t>
         </is>
       </c>
       <c r="G893" t="inlineStr"/>
@@ -40813,12 +40845,12 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>3.2 V6 Quattro</t>
+          <t>2.0 TFSI</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>2006-01 ~ 2010-01</t>
+          <t>2006-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
@@ -40828,7 +40860,7 @@
       </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>AAQ</t>
+          <t>AAR, ABM, ABT</t>
         </is>
       </c>
       <c r="G894" t="inlineStr"/>
@@ -40849,12 +40881,12 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>3.2 VR6 Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
         <is>
-          <t>2003-01 ~ 2006-01</t>
+          <t>2006-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E895" t="inlineStr">
@@ -40864,7 +40896,7 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>ABC, ABO, ABU</t>
         </is>
       </c>
       <c r="G895" t="inlineStr"/>
@@ -40885,12 +40917,12 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>40 TFSI</t>
+          <t>3.2 V6 Quattro</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
         <is>
-          <t>2018-01 ~ 至今</t>
+          <t>2006-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E896" t="inlineStr">
@@ -40900,7 +40932,7 @@
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>AAQ</t>
         </is>
       </c>
       <c r="G896" t="inlineStr"/>
@@ -40921,12 +40953,12 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>45 TFSI</t>
+          <t>3.2 VR6 Quattro</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>2018-01 ~ 至今</t>
+          <t>2003-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E897" t="inlineStr">
@@ -40936,7 +40968,7 @@
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>310</t>
         </is>
       </c>
       <c r="G897" t="inlineStr"/>
@@ -40957,7 +40989,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>45 TFSI Quattro</t>
+          <t>40 TFSI</t>
         </is>
       </c>
       <c r="D898" t="inlineStr">
@@ -40972,7 +41004,7 @@
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>ACJ</t>
+          <t>ACH</t>
         </is>
       </c>
       <c r="G898" t="inlineStr"/>
@@ -40988,49 +41020,33 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>TT RS Coupe</t>
+          <t>TT Coupe</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>2.5 TFSI Quattro</t>
+          <t>45 TFSI</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>2009-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>8307, 7967, 1860</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
         <is>
-          <t>ABH, ABN, ABS, AAD</t>
-        </is>
-      </c>
-      <c r="G899" t="inlineStr">
-        <is>
-          <t>01/2016 -</t>
-        </is>
-      </c>
-      <c r="H899" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I899" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J899" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr"/>
+      <c r="I899" t="inlineStr"/>
+      <c r="J899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -41040,17 +41056,17 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>TT RS Plus Coupe</t>
+          <t>TT Coupe</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>2.5 TFSI Quattro</t>
+          <t>45 TFSI Quattro</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2013-01</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -41060,7 +41076,7 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>ABR</t>
+          <t>ACJ</t>
         </is>
       </c>
       <c r="G900" t="inlineStr"/>
@@ -41076,7 +41092,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>TT RS Plus Roadster</t>
+          <t>TT RS Coupe</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -41086,23 +41102,39 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>2012-01 ~ 2013-01</t>
+          <t>2009-01 ~ 至今</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8307, 7967, 1860</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
         <is>
-          <t>ABS</t>
-        </is>
-      </c>
-      <c r="G901" t="inlineStr"/>
-      <c r="H901" t="inlineStr"/>
-      <c r="I901" t="inlineStr"/>
-      <c r="J901" t="inlineStr"/>
+          <t>ABH, ABN, ABS, AAD</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>01/2016 -</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -41112,7 +41144,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>TT RS Roadster</t>
+          <t>TT RS Plus Coupe</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -41122,39 +41154,23 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>2009-01 ~ 至今</t>
+          <t>2012-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>8307, 7967, 1860</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
         <is>
-          <t>ABI, ABO, ABT, AAE</t>
-        </is>
-      </c>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>01/2016 -</t>
-        </is>
-      </c>
-      <c r="H902" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I902" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J902" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -41164,17 +41180,17 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>TT Roadster</t>
+          <t>TT RS Plus Roadster</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>1.8 T</t>
+          <t>2.5 TFSI Quattro</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>1999-01 ~ 2006-01</t>
+          <t>2012-01 ~ 2013-01</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
@@ -41184,7 +41200,7 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>303, 306, 316, 317</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="G903" t="inlineStr"/>
@@ -41200,33 +41216,49 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>TT Roadster</t>
+          <t>TT RS Roadster</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>1.8 T Quattro</t>
+          <t>2.5 TFSI Quattro</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>1999-01 ~ 2006-01</t>
+          <t>2009-01 ~ 至今</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>7967, 8307</t>
+          <t>8307, 7967, 1860</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
         <is>
-          <t>315, 304, 305, 308</t>
-        </is>
-      </c>
-      <c r="G904" t="inlineStr"/>
-      <c r="H904" t="inlineStr"/>
-      <c r="I904" t="inlineStr"/>
-      <c r="J904" t="inlineStr"/>
+          <t>ABI, ABO, ABT, AAE</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>01/2016 -</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -41241,12 +41273,12 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>1.8 TFSI</t>
+          <t>1.8 T</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2018-01</t>
+          <t>1999-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E905" t="inlineStr">
@@ -41256,7 +41288,7 @@
       </c>
       <c r="F905" t="inlineStr">
         <is>
-          <t>ABB, ACC</t>
+          <t>303, 306, 316, 317</t>
         </is>
       </c>
       <c r="G905" t="inlineStr"/>
@@ -41277,22 +41309,22 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>2.0 TDI Quattro</t>
+          <t>1.8 T Quattro</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>2008-01 ~ 2014-01</t>
+          <t>1999-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7967, 8307</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>ABF</t>
+          <t>315, 304, 305, 308</t>
         </is>
       </c>
       <c r="G906" t="inlineStr"/>
@@ -41313,12 +41345,12 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>2.0 TDI ultra</t>
+          <t>1.8 TFSI</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>2014-01 ~ 2018-01</t>
+          <t>2008-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
@@ -41328,7 +41360,7 @@
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>ACA</t>
+          <t>ABB, ACC</t>
         </is>
       </c>
       <c r="G907" t="inlineStr"/>
@@ -41349,12 +41381,12 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>2.0 TDI ultra Quattro</t>
+          <t>2.0 TDI Quattro</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>2017-01 ~ 2018-01</t>
+          <t>2008-01 ~ 2014-01</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
@@ -41364,7 +41396,7 @@
       </c>
       <c r="F908" t="inlineStr">
         <is>
-          <t>ACG</t>
+          <t>ABF</t>
         </is>
       </c>
       <c r="G908" t="inlineStr"/>
@@ -41385,12 +41417,12 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>2.0 TFSI</t>
+          <t>2.0 TDI ultra</t>
         </is>
       </c>
       <c r="D909" t="inlineStr">
         <is>
-          <t>2007-01 ~ 2018-01</t>
+          <t>2014-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E909" t="inlineStr">
@@ -41400,7 +41432,7 @@
       </c>
       <c r="F909" t="inlineStr">
         <is>
-          <t>AAS, ABN, ABX</t>
+          <t>ACA</t>
         </is>
       </c>
       <c r="G909" t="inlineStr"/>
@@ -41421,12 +41453,12 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>2.0 TDI ultra Quattro</t>
         </is>
       </c>
       <c r="D910" t="inlineStr">
         <is>
-          <t>2007-01 ~ 2018-01</t>
+          <t>2017-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E910" t="inlineStr">
@@ -41436,7 +41468,7 @@
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>ABD, ABP, ABY</t>
+          <t>ACG</t>
         </is>
       </c>
       <c r="G910" t="inlineStr"/>
@@ -41457,12 +41489,12 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>3.2 V6 Quattro</t>
+          <t>2.0 TFSI</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
         <is>
-          <t>2007-01 ~ 2010-01</t>
+          <t>2007-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
@@ -41472,7 +41504,7 @@
       </c>
       <c r="F911" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>AAS, ABN, ABX</t>
         </is>
       </c>
       <c r="G911" t="inlineStr"/>
@@ -41493,12 +41525,12 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>3.2 VR6 Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
         <is>
-          <t>2003-01 ~ 2006-01</t>
+          <t>2007-01 ~ 2018-01</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
@@ -41508,7 +41540,7 @@
       </c>
       <c r="F912" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>ABD, ABP, ABY</t>
         </is>
       </c>
       <c r="G912" t="inlineStr"/>
@@ -41529,12 +41561,12 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>40 TFSI</t>
+          <t>3.2 V6 Quattro</t>
         </is>
       </c>
       <c r="D913" t="inlineStr">
         <is>
-          <t>2018-01 ~ 至今</t>
+          <t>2007-01 ~ 2010-01</t>
         </is>
       </c>
       <c r="E913" t="inlineStr">
@@ -41544,7 +41576,7 @@
       </c>
       <c r="F913" t="inlineStr">
         <is>
-          <t>ACL</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="G913" t="inlineStr"/>
@@ -41565,12 +41597,12 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>45 TFSI</t>
+          <t>3.2 VR6 Quattro</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
         <is>
-          <t>2018-01 ~ 至今</t>
+          <t>2003-01 ~ 2006-01</t>
         </is>
       </c>
       <c r="E914" t="inlineStr">
@@ -41580,7 +41612,7 @@
       </c>
       <c r="F914" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>311</t>
         </is>
       </c>
       <c r="G914" t="inlineStr"/>
@@ -41601,7 +41633,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>45 TFSI Quattro</t>
+          <t>40 TFSI</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -41616,7 +41648,7 @@
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ACL</t>
         </is>
       </c>
       <c r="G915" t="inlineStr"/>
@@ -41632,17 +41664,17 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>TTS Coupe</t>
+          <t>TT Roadster</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>45 TFSI</t>
         </is>
       </c>
       <c r="D916" t="inlineStr">
         <is>
-          <t>2008-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
@@ -41652,7 +41684,7 @@
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>AAU, ABV, ACD, ACK, ACP</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="G916" t="inlineStr"/>
@@ -41668,17 +41700,17 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>TTS Roadster</t>
+          <t>TT Roadster</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>2.0 TFSI Quattro</t>
+          <t>45 TFSI Quattro</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>2008-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
@@ -41688,7 +41720,7 @@
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>AAV, ABZ, ACE, ACO, ACQ</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="G917" t="inlineStr"/>
@@ -41704,27 +41736,27 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>TTS Coupe</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>3.5 Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>1988-01 ~ 1994-01</t>
+          <t>2008-01 ~ 至今</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>AAU, ABV, ACD, ACK, ACP</t>
         </is>
       </c>
       <c r="G918" t="inlineStr"/>
@@ -41740,27 +41772,27 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>TTS Roadster</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>3.6 Quattro</t>
+          <t>2.0 TFSI Quattro</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
         <is>
-          <t>1988-01 ~ 1994-01</t>
+          <t>2008-01 ~ 至今</t>
         </is>
       </c>
       <c r="E919" t="inlineStr">
         <is>
-          <t>0588</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
         <is>
-          <t>431, 577</t>
+          <t>AAV, ABZ, ACE, ACO, ACQ</t>
         </is>
       </c>
       <c r="G919" t="inlineStr"/>
@@ -41781,12 +41813,12 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>4.2 Quattro</t>
+          <t>3.5 Quattro</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
         <is>
-          <t>1991-01 ~ 1994-01</t>
+          <t>1988-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E920" t="inlineStr">
@@ -41796,7 +41828,7 @@
       </c>
       <c r="F920" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>431</t>
         </is>
       </c>
       <c r="G920" t="inlineStr"/>
@@ -41812,17 +41844,17 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>e-tron</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>50 Quattro</t>
+          <t>3.6 Quattro</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2022-01</t>
+          <t>1988-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
@@ -41832,29 +41864,13 @@
       </c>
       <c r="F921" t="inlineStr">
         <is>
-          <t>BSK</t>
-        </is>
-      </c>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>09/2018 -</t>
-        </is>
-      </c>
-      <c r="H921" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I921" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J921" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>431, 577</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="inlineStr"/>
+      <c r="J921" t="inlineStr"/>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -41864,17 +41880,17 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>e-tron</t>
+          <t>V8</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>55 Quattro</t>
+          <t>4.2 Quattro</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>2019-01 ~ 2022-01</t>
+          <t>1991-01 ~ 1994-01</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
@@ -41884,29 +41900,13 @@
       </c>
       <c r="F922" t="inlineStr">
         <is>
-          <t>BPG</t>
-        </is>
-      </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>09/2018 -</t>
-        </is>
-      </c>
-      <c r="H922" t="inlineStr">
-        <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
-        </is>
-      </c>
-      <c r="I922" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J922" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -41921,7 +41921,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>S Quattro</t>
+          <t>50 Quattro</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
@@ -41936,7 +41936,7 @@
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>BVM</t>
+          <t>BSK</t>
         </is>
       </c>
       <c r="G923" t="inlineStr">
@@ -41968,17 +41968,17 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>e-tron GT</t>
+          <t>e-tron</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>Quattro</t>
+          <t>55 Quattro</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>2021-01 ~ 至今</t>
+          <t>2019-01 ~ 2022-01</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -41988,17 +41988,17 @@
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>BZL, CEW</t>
+          <t>BPG</t>
         </is>
       </c>
       <c r="G924" t="inlineStr">
         <is>
-          <t>10/2020 - 08/2024, 09/2024 -</t>
+          <t>09/2018 -</t>
         </is>
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -42020,7 +42020,7 @@
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>e-tron GT</t>
+          <t>e-tron</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
@@ -42030,7 +42030,7 @@
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2020-01 ~ 2022-01</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -42040,17 +42040,17 @@
       </c>
       <c r="F925" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BVM</t>
         </is>
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>09/2024 -</t>
+          <t>09/2018 -</t>
         </is>
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>RDE254+RDV021, RDE254+RDV026</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -42072,17 +42072,17 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>e-tron Sportback</t>
+          <t>e-tron GT</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>50 Quattro</t>
+          <t>Quattro</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2022-01</t>
+          <t>2021-01 ~ 至今</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -42092,17 +42092,17 @@
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>BSM</t>
+          <t>BZL, CEW</t>
         </is>
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>10/2020 - 08/2024, 09/2024 -</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047, RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -42124,17 +42124,17 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>e-tron Sportback</t>
+          <t>e-tron GT</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>55 Quattro</t>
+          <t>S Quattro</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>2020-01 ~ 2022-01</t>
+          <t>2024-01 ~ 至今</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -42144,17 +42144,17 @@
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>BSN</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="G927" t="inlineStr">
         <is>
-          <t>09/2018 -</t>
+          <t>09/2024 -</t>
         </is>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+          <t>RDE254+RDV021, RDE254+RDV026</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
@@ -42181,40 +42181,144 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
+          <t>50 Quattro</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2022-01</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>0588</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>BSM</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>09/2018 -</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>AUDI</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>e-tron Sportback</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>55 Quattro</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2022-01</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>0588</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>BSN</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>09/2018 -</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>AUDI</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>e-tron Sportback</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
           <t>S Quattro</t>
         </is>
       </c>
-      <c r="D928" t="inlineStr">
+      <c r="D930" t="inlineStr">
         <is>
           <t>2020-01 ~ 2022-01</t>
         </is>
       </c>
-      <c r="E928" t="inlineStr">
-        <is>
-          <t>0588</t>
-        </is>
-      </c>
-      <c r="F928" t="inlineStr">
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>0588</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
         <is>
           <t>BVN</t>
         </is>
       </c>
-      <c r="G928" t="inlineStr">
+      <c r="G930" t="inlineStr">
         <is>
           <t>09/2018 -</t>
         </is>
       </c>
-      <c r="H928" t="inlineStr">
+      <c r="H930" t="inlineStr">
         <is>
           <t>RDE047 + RDV021 | 45.142.000, RDE047 + RDV026 | 73.907.047</t>
         </is>
       </c>
-      <c r="I928" t="inlineStr">
-        <is>
-          <t>BH SENS</t>
-        </is>
-      </c>
-      <c r="J928" t="inlineStr">
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>BH SENS</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
         <is>
           <t>433</t>
         </is>
